--- a/SGC-CKN/Excel/abdc7e82-eb90-49ae-8e1e-a5f99919c4c8_Nhà_hát_382_D1200_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/abdc7e82-eb90-49ae-8e1e-a5f99919c4c8_Nhà_hát_382_D1200_05-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -103,7 +103,7 @@
 04/04/2026</t>
   </si>
   <si>
-    <t>Chiều dài tính từ đỉnh casing 1.34 đến 6.8</t>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -114,9 +114,6 @@
   <si>
     <t xml:space="preserve">22:20
 04/04/2026</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>3</t>
@@ -1280,24 +1277,24 @@
         <v>1.26</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>34</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>35</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="13">
         <v>-7.85</v>
@@ -1315,24 +1312,24 @@
         <v>5.23</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="D14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-20.48</v>
@@ -1350,24 +1347,24 @@
         <v>5.31</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-28.45</v>
@@ -1385,24 +1382,24 @@
         <v>6.05</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>45</v>
-      </c>
       <c r="E16" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="22">
         <v>-34</v>
@@ -1420,24 +1417,24 @@
         <v>16.96</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-38.24</v>
@@ -1455,24 +1452,24 @@
         <v>2.57</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>50</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>51</v>
       </c>
       <c r="F18" s="28">
         <v>-56.54</v>
@@ -1490,24 +1487,24 @@
         <v>0.95</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="33" t="s">
+      <c r="D19" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="34" t="s">
         <v>54</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>55</v>
       </c>
       <c r="F19" s="32">
         <v>-60.13</v>
@@ -1525,24 +1522,24 @@
         <v>3.79</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
+      <c r="D20" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>57</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>58</v>
       </c>
       <c r="F20" s="35">
         <v>-65.5</v>
@@ -1560,24 +1557,24 @@
         <v>3.9</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>60</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>61</v>
       </c>
       <c r="F21" s="16">
         <v>-68.1</v>
@@ -1595,12 +1592,12 @@
         <v>0.97</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="38"/>
       <c r="C24" s="38"/>
@@ -1706,31 +1703,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1799,7 +1796,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1828,7 +1825,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1857,7 +1854,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1886,7 +1883,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1915,7 +1912,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1944,7 +1941,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1973,7 +1970,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -2002,7 +1999,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
@@ -2031,7 +2028,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" s="16">
         <v>1</v>
@@ -2054,13 +2051,13 @@
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D13" s="40">
         <v>11</v>

--- a/SGC-CKN/Excel/abdc7e82-eb90-49ae-8e1e-a5f99919c4c8_Nhà_hát_382_D1200_05-04-2026.xlsx
+++ b/SGC-CKN/Excel/abdc7e82-eb90-49ae-8e1e-a5f99919c4c8_Nhà_hát_382_D1200_05-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>382</t>
+    <t>P382</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
